--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>824614</v>
+        <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96426</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>RIDDARHUSET - V OM KULAN (07G3a01), Ög</t>
+          <t>Ljungbacka, 645 m SO, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552484</v>
+        <v>552386</v>
       </c>
       <c r="R2" t="n">
-        <v>6413685</v>
+        <v>6413821</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-04-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-04-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>070630011 / ANTI CUR / Enstaka-sparsam (1)  / OBJ.AREA:6,6 ha</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,35 +770,41 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>bergbrant i vägkant</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Ek</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
-        </is>
-      </c>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/824614</t>
+          <t>https://artportalen.se/Sighting/137232142</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1855509</v>
+        <v>824614</v>
       </c>
       <c r="B3" t="n">
-        <v>83290</v>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -866,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>070630011 / CHA BRAC / Enstaka-sparsam (1)  / OBJ.AREA:6,6 ha</t>
+          <t>070630011 / ANTI CUR / Enstaka-sparsam (1)  / OBJ.AREA:6,6 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,16 +906,16 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1855509</t>
+          <t>https://artportalen.se/Sighting/824614</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7256340</v>
+        <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>96692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,41 +923,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100077</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnedebäcken vid Kulan, Ög</t>
+          <t>Ljungbacka, 565 m SO, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552652</v>
+        <v>552347</v>
       </c>
       <c r="R4" t="n">
-        <v>6413461</v>
+        <v>6413895</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,12 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-09-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,31 +993,41 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>bergbrant i vägkant</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>naken jord</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mathias Ibbe</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mathias Ibbe</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7256340</t>
+          <t>https://artportalen.se/Sighting/137232151</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6784679</v>
+        <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>97985</v>
+        <v>96497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,33 +1035,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224363</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NR Granskogsravinen i Flytthem, Ög</t>
+          <t>Ljungbacka, 635 m SO, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552432</v>
+        <v>552414</v>
       </c>
       <c r="R5" t="n">
-        <v>6413906</v>
+        <v>6413855</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,12 +1089,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-06-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-06-07</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>stenstolpar av granit i vägräcke</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,20 +1110,562 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>fuktig granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Urban Ekstam</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Urban Ekstam</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137232102</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137232125</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ljungbacka, 725 m SO, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552395</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6413730</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>vägkant mot brant gammal granskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>naken jord</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137232125</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1855509</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>RIDDARHUSET - V OM KULAN (07G3a01), Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552484</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6413685</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1995-04-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1995-04-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>070630011 / CHA BRAC / Enstaka-sparsam (1)  / OBJ.AREA:6,6 ha</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1855509</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7256340</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finnedebäcken vid Kulan, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552652</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6413461</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mathias Ibbe</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mathias Ibbe</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7256340</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137232117</v>
+      </c>
+      <c r="B9" t="n">
+        <v>111368</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ljungbacka, 750 m SO, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552393</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6413701</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>klipphylla i brant vägskärning</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137232117</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6784679</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NR Granskogsravinen i Flytthem, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552432</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6413906</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2013-06-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2013-06-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Urban Ekstam</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Urban Ekstam</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6784679</t>
         </is>
@@ -1113,6 +1677,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96497</v>
+        <v>96499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,6 +1497,9 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ljungbacka, 750 m SO, Ög</t>
@@ -1547,6 +1550,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1563,7 +1567,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96499</v>
+        <v>96502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96502</v>
+        <v>96512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
+          <t>Anders Svenson, Jimmie Rundberg, Tommy Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96512</v>
+        <v>96513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
+          <t>Anders Svenson, Jimmie Rundberg, Tommy Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson, Jimmie Rundberg, Tommy Nilsson</t>
+          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Svenson, Jimmie Rundberg, Tommy Nilsson</t>
+          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96513</v>
+        <v>96518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96518</v>
+        <v>96520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96520</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96538</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21473-2022 artfynd.xlsx
+++ b/artfynd/A 21473-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137232142</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137232151</v>
       </c>
       <c r="B4" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137232102</v>
       </c>
       <c r="B5" t="n">
-        <v>96542</v>
+        <v>96546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137232125</v>
       </c>
       <c r="B6" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137232117</v>
       </c>
       <c r="B9" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
